--- a/ДЗ_1_терминал.xlsx
+++ b/ДЗ_1_терминал.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Алексей\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\QA\git\group_25_test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{427E1406-218D-4D5A-8AC6-C41BBBF38663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43794585-C6FF-456E-A794-273BE3444D77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="51">
   <si>
     <t>Номер</t>
   </si>
@@ -130,9 +130,6 @@
     <t>просмотреть содержимое в реальном времени (команда grep) изучите как она работает</t>
   </si>
   <si>
-    <t>tail file_1234567890.txt</t>
-  </si>
-  <si>
     <t>вывести несколько первых строк из текстового файла</t>
   </si>
   <si>
@@ -182,6 +179,12 @@
   </si>
   <si>
     <t>запустить скрипт: ./file_script.txt</t>
+  </si>
+  <si>
+    <t>mkdir {dir_4,dir_5,dir_6}</t>
+  </si>
+  <si>
+    <t>tail -f file_1234567890.txt</t>
   </si>
 </sst>
 </file>
@@ -621,7 +624,7 @@
         <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>10</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -720,7 +723,7 @@
         <v>31</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -728,10 +731,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" t="s">
         <v>33</v>
-      </c>
-      <c r="C18" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -739,10 +742,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>35</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -750,10 +753,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -761,15 +764,15 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>38</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="24" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -777,10 +780,10 @@
         <v>1</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>42</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -788,25 +791,25 @@
         <v>2</v>
       </c>
       <c r="B25" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C25" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C26" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C27" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C28" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -816,7 +819,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C30" t="s">
-        <v>10</v>
+        <v>49</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -846,7 +849,7 @@
     </row>
     <row r="36" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C36" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/ДЗ_1_терминал.xlsx
+++ b/ДЗ_1_терминал.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\QA\git\group_25_test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43794585-C6FF-456E-A794-273BE3444D77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80DE56D2-CD4E-4FC9-81A1-465077B59D20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="52">
   <si>
     <t>Номер</t>
   </si>
@@ -185,6 +185,9 @@
   </si>
   <si>
     <t>tail -f file_1234567890.txt</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -770,6 +773,11 @@
         <v>38</v>
       </c>
     </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C22" t="s">
+        <v>51</v>
+      </c>
+    </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>40</v>
